--- a/visa/20012026/autosave_temp.xlsx
+++ b/visa/20012026/autosave_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,102 +476,135 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BACH HOA XANH</t>
+          <t>Bánh Mì, Cơm Tấm &amp; Đồ Chay Cô Hương - 411/58/7A Lê Đức Thọ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Siêu thị Bách hóa XANH Huỳnh Tấn Phát</t>
+          <t>Bánh Mì Chay Cô Hương</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>665-667 Huỳnh Tấn Phát, Tân Thuận Đông, Quận 7, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>411/58 Đ. Lê Đức Thọ, Phường 17, Gò Vấp, Thành phố Hồ Chí Minh 727010, Việt Nam</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>+8419001908</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.bachhoaxanh.com/</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>{"Thứ Hai": "06:30–21:30", "Thứ Ba": "06:30–21:30", "Thứ Tư": "06:30–21:30", "Thứ Năm": "06:30–21:30", "Thứ Sáu": "06:30–21:30", "Thứ Bảy": "06:30–21:30", "Chủ Nhật": "06:30–21:30"}</t>
+          <t>{"Thứ Hai": "", "Thứ Ba": "", "Thứ Tư": "", "Thứ Năm": "", "Thứ Sáu": "", "Thứ Bảy": "", "Chủ Nhật": ""}</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.7381125</t>
+          <t>10.8421558</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>106.7304222</t>
+          <t>106.672913</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Si%C3%AAu+th%E1%BB%8B+B%C3%A1ch+h%C3%B3a+XANH+Hu%E1%BB%B3nh+T%E1%BA%A5n+Ph%C3%A1t/@10.7381125,106.7304222,17z/data=!3m1!4b1!4m6!3m5!1s0x31752546754f2da1:0x611eda4169abdcfe!8m2!3d10.7381125!4d106.7304222!16s%2Fg%2F11sb2srq33?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDExOS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/B%C3%A1nh+M%C3%AC+Chay+C%C3%B4+H%C6%B0%C6%A1ng/@10.8421558,106.672913,17z/data=!3m1!4b1!4m6!3m5!1s0x317529004bf7ae97:0x55164838b4af2c82!8m2!3d10.8421558!4d106.672913!16s%2Fg%2F11ylf8kvwq!10m3!1e1!2e18!4e1?entry=ttu&amp;g_ep=EgoyMDI2MDIwMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HOKKAIDO Q1</t>
+          <t>Mì Dầu Hào HongKong Thượng Hạng 港式蚝油捞面 - ChaChaanTeng - Phan Phú Tiên</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sushi Nishitsugu Omakase</t>
+          <t>Hào Huê Quán - Dimsum &amp; Alacarte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>108 Pasteur, Bến Nghé, Quận 1, Thành phố Hồ Chí Minh 72914, Việt Nam</t>
+          <t>412 Trần Phú, Phường 7, Quận 5, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+84862058800</t>
+          <t>+84797881386</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Sushi-Nishitsugu-116053091404543</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t></t>
-        </is>
-      </c>
+          <t>https://haohue.cukcuk.vn/order-online</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>{"Thứ Hai": "17:30–22:30", "Thứ Ba": "Đóng cửa", "Thứ Tư": "17:30–22:30", "Thứ Năm": "17:30–22:30", "Thứ Sáu": "17:30–22:30", "Thứ Bảy": "17:30–22:30", "Chủ Nhật": "17:30–22:30"}</t>
+          <t>{"Thứ Hai": "07:00–14:0016:30–22:00", "Thứ Ba": "07:00–14:0016:30–22:00", "Thứ Tư": "07:00–14:0016:30–22:00", "Thứ Năm": "07:00–14:0016:30–22:00", "Thứ Sáu": "07:00–14:0016:30–22:00", "Thứ Bảy": "07:00–14:0016:30–22:00", "Chủ Nhật": "07:00–14:0016:30–22:00"}</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.7728517</t>
+          <t>10.7529381</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>106.7018409</t>
+          <t>106.668225</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sushi+Nishitsugu+Omakase/@10.7728517,106.7018409,17z/data=!3m1!4b1!4m6!3m5!1s0x317525aec7379a0d:0xda253cd94bf3cf9e!8m2!3d10.7728517!4d106.7018409!16s%2Fg%2F11txfrj0bn?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDExOS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/H%C3%A0o+Hu%C3%AA+Qu%C3%A1n+-+Dimsum+%26+Alacarte/@10.7529381,106.668225,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f500ba50187:0x56e5ee992cf4214b!8m2!3d10.7529381!4d106.668225!16s%2Fg%2F11rc4bssnv?authuser=0&amp;hl=vi&amp;entry=ttu&amp;g_ep=EgoyMDI2MDIwMy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Đậu Hủ Cá Viên HongKong 港式鱼丸豆腐 - ChaChaanTeng</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Đậu hũ thúi Đài Loan KỲ LONG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>247/20 Lạc Long Quân, Phường 3, Quận 11, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+84834568830</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>{"Thứ Hai": "15:00–22:00", "Thứ Ba": "15:00–22:00", "Thứ Tư": "15:00–22:00", "Thứ Năm": "15:00–22:00", "Thứ Sáu": "15:00–22:00", "Thứ Bảy": "15:00–22:00", "Chủ Nhật": "15:00–22:00"}</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10.7646086</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>106.6417212</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/%C4%90%E1%BA%ADu+h%C5%A9+th%C3%BAi+%C4%90%C3%A0i+Loan+K%E1%BB%B2+LONG/@10.7646086,106.6417212,17z/data=!3m1!4b1!4m6!3m5!1s0x31752f9287c59cd7:0xd014667c3c440ae4!8m2!3d10.7646086!4d106.6417212!16s%2Fg%2F11n5hy56tw?entry=ttu&amp;g_ep=EgoyMDI2MDIwMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
     </row>
